--- a/data/trans_dic/IP12B$hueso-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$hueso-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,92</t>
+          <t>0,0; 19,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,97</t>
+          <t>0,0; 22,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,11</t>
+          <t>0,0; 14,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 28,16</t>
+          <t>3,47; 24,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,99</t>
+          <t>0,0; 20,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,97</t>
+          <t>0,0; 15,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 17,18</t>
+          <t>1,91; 17,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 12,82</t>
+          <t>1,61; 13,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,34</t>
+          <t>0,0; 10,01</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,03</t>
+          <t>0,0; 38,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,91</t>
+          <t>0,0; 32,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,3</t>
+          <t>0,0; 37,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,81</t>
+          <t>0,0; 45,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,97</t>
+          <t>5,35; 41,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,33</t>
+          <t>0,0; 29,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,13; 25,42</t>
+          <t>3,2; 27,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 27,45</t>
+          <t>5,04; 27,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 26,67</t>
+          <t>2,7; 26,29</t>
         </is>
       </c>
     </row>
@@ -1007,32 +1008,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,01</t>
+          <t>0,0; 44,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 54,55</t>
+          <t>7,35; 55,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,52</t>
+          <t>0,0; 45,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 39,47</t>
+          <t>4,34; 36,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,27</t>
+          <t>0,0; 40,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1042,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,2; 35,49</t>
+          <t>8,72; 37,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 30,87</t>
+          <t>0,0; 34,2</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,91; 16,65</t>
+          <t>2,95; 16,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 13,9</t>
+          <t>2,72; 15,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 12,97</t>
+          <t>2,58; 13,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 15,09</t>
+          <t>1,78; 15,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 16,86</t>
+          <t>5,07; 17,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 14,22</t>
+          <t>1,46; 13,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 12,07</t>
+          <t>3,53; 12,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,84; 12,84</t>
+          <t>4,83; 13,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 11,64</t>
+          <t>3,15; 10,96</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1489</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2713</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2385</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3198</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4614</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3379</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>681; 4884</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5162</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2899</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>683; 6131</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>729; 6003</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4100</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1387</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1429</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1929</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2219</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3194</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2790</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4123</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4459</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4530</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>547; 4277</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4172</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>663; 5675</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1221; 6712</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>704; 6854</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2175</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1441</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2632</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4808</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2205</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3515</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>667; 5013</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3892</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>651; 5463</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3341</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4107</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2097; 9025</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5704</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3398</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4335</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3546</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2904</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6051</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2768</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6302</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>10386</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>6314</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1294; 7435</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1665; 9378</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1420; 7590</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>830; 7190</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3225; 11208</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>699; 6273</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3197; 11372</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>6027; 16679</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3241; 11283</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$hueso-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$hueso-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,91</t>
+          <t>0,0; 22,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,79</t>
+          <t>0,0; 18,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,87</t>
+          <t>0,0; 16,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 24,89</t>
+          <t>3,45; 27,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,55</t>
+          <t>0,0; 18,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,89</t>
+          <t>0,0; 18,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 17,18</t>
+          <t>1,97; 17,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 13,23</t>
+          <t>1,62; 14,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,01</t>
+          <t>0,0; 11,46</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,38</t>
+          <t>0,0; 34,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,22</t>
+          <t>0,0; 28,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,07</t>
+          <t>0,0; 39,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,45</t>
+          <t>0,0; 35,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,35; 41,84</t>
+          <t>5,22; 47,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,7</t>
+          <t>0,0; 30,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 27,4</t>
+          <t>3,19; 27,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,04; 27,7</t>
+          <t>5,15; 27,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 26,29</t>
+          <t>2,57; 24,77</t>
         </is>
       </c>
     </row>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,24</t>
+          <t>0,0; 49,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 55,24</t>
+          <t>7,34; 55,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,74</t>
+          <t>0,0; 48,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,27 +1028,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,34; 36,46</t>
+          <t>4,4; 37,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,89</t>
+          <t>0,0; 52,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,1</t>
+          <t>0,0; 28,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,72; 37,51</t>
+          <t>8,66; 35,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,2</t>
+          <t>3,65; 31,83</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 16,95</t>
+          <t>2,99; 17,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 15,3</t>
+          <t>2,54; 16,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 13,77</t>
+          <t>2,4; 14,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 15,39</t>
+          <t>1,53; 14,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,07; 17,63</t>
+          <t>4,91; 17,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,11</t>
+          <t>1,45; 13,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 12,55</t>
+          <t>3,57; 12,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,83; 13,36</t>
+          <t>5,06; 13,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 10,96</t>
+          <t>2,81; 10,86</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3198</t>
+          <t>0; 3545</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4614</t>
+          <t>0; 3663</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3379</t>
+          <t>0; 3777</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>681; 4884</t>
+          <t>677; 5485</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5162</t>
+          <t>0; 4599</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2899</t>
+          <t>0; 3289</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>683; 6131</t>
+          <t>702; 6194</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>729; 6003</t>
+          <t>735; 6361</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4100</t>
+          <t>0; 4694</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4123</t>
+          <t>0; 3674</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4515</t>
+          <t>0; 3959</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4459</t>
+          <t>0; 4756</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4530</t>
+          <t>0; 3572</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>547; 4277</t>
+          <t>534; 4814</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4172</t>
+          <t>0; 4227</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>663; 5675</t>
+          <t>660; 5688</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1221; 6712</t>
+          <t>1249; 6722</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>704; 6854</t>
+          <t>670; 6457</t>
         </is>
       </c>
     </row>
@@ -1906,17 +1906,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3515</t>
+          <t>0; 3962</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>667; 5013</t>
+          <t>666; 5053</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3892</t>
+          <t>0; 4131</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1926,27 +1926,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>651; 5463</t>
+          <t>659; 5611</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3341</t>
+          <t>0; 4272</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4107</t>
+          <t>0; 4505</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2097; 9025</t>
+          <t>2083; 8450</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5704</t>
+          <t>608; 5310</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1294; 7435</t>
+          <t>1310; 7500</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1665; 9378</t>
+          <t>1559; 9850</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1420; 7590</t>
+          <t>1321; 8031</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>830; 7190</t>
+          <t>713; 6839</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3225; 11208</t>
+          <t>3124; 10867</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>699; 6273</t>
+          <t>692; 6592</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3197; 11372</t>
+          <t>3234; 11278</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6027; 16679</t>
+          <t>6323; 17173</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3241; 11283</t>
+          <t>2894; 11188</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$hueso-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$hueso-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10,56%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>4,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>4,43%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,97%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10,56%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,07</t>
+          <t>3,46; 28,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,1</t>
+          <t>0,0; 18,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,62</t>
+          <t>0,0; 14,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 27,95</t>
+          <t>0,0; 20,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,31</t>
+          <t>0,0; 20,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,02</t>
+          <t>0,0; 15,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 17,36</t>
+          <t>1,92; 17,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 14,02</t>
+          <t>1,61; 12,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,46</t>
+          <t>0,0; 11,34</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8,35%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18,87%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,69%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>12,91%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>9,03%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>11,88%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18,87%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,2</t>
+          <t>0,0; 31,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,25</t>
+          <t>0,0; 46,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,54</t>
+          <t>0,0; 30,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,84</t>
+          <t>0,0; 39,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 47,1</t>
+          <t>0,0; 27,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,1</t>
+          <t>0,0; 34,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 27,46</t>
+          <t>3,13; 25,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 27,74</t>
+          <t>5,2; 27,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 24,77</t>
+          <t>2,97; 26,67</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17,57%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,35%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>17,24%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>23,97%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>16,93%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17,57%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,34; 55,69</t>
+          <t>4,49; 39,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,55</t>
+          <t>0,0; 39,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 51,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 37,44</t>
+          <t>7,35; 54,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,29</t>
+          <t>0,0; 49,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,63</t>
+          <t>0,0; 26,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,66; 35,12</t>
+          <t>8,2; 35,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 31,83</t>
+          <t>3,65; 30,87</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>7,74%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>7,07%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>6,43%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9,52%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 17,09</t>
+          <t>1,5; 15,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 16,07</t>
+          <t>4,19; 16,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 14,57</t>
+          <t>1,4; 14,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 14,64</t>
+          <t>2,91; 16,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 17,1</t>
+          <t>2,48; 13,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 13,77</t>
+          <t>1,54; 12,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 12,45</t>
+          <t>3,64; 12,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,06; 13,76</t>
+          <t>4,84; 12,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,81; 10,86</t>
+          <t>2,74; 11,64</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1474,27 +1474,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1489</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>676</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1489</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3545</t>
+          <t>679; 5526</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3663</t>
+          <t>0; 4769</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3777</t>
+          <t>0; 2731</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>677; 5485</t>
+          <t>0; 3359</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4599</t>
+          <t>0; 4245</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3289</t>
+          <t>0; 3434</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>702; 6194</t>
+          <t>685; 6130</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>735; 6361</t>
+          <t>729; 5814</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4694</t>
+          <t>0; 4645</t>
         </is>
       </c>
     </row>
@@ -1637,27 +1637,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1929</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1387</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1265</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1429</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>832</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1929</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1360</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3674</t>
+          <t>0; 3171</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3959</t>
+          <t>0; 4801</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4756</t>
+          <t>0; 4260</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3572</t>
+          <t>0; 4193</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>534; 4814</t>
+          <t>0; 3910</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4227</t>
+          <t>0; 4125</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>660; 5688</t>
+          <t>648; 5265</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1249; 6722</t>
+          <t>1261; 6652</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>670; 6457</t>
+          <t>775; 6954</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2632</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1369</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2175</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1441</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2632</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>764</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3962</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>666; 5053</t>
+          <t>672; 5915</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4131</t>
+          <t>0; 3208</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4053</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>659; 5611</t>
+          <t>667; 4950</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4272</t>
+          <t>0; 4214</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4505</t>
+          <t>0; 4108</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2083; 8450</t>
+          <t>1972; 8538</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>608; 5310</t>
+          <t>609; 5149</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2904</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6051</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2768</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>3398</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>4335</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3546</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2904</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6051</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2768</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1310; 7500</t>
+          <t>702; 7047</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1559; 9850</t>
+          <t>2662; 10719</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1321; 8031</t>
+          <t>669; 6806</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>713; 6839</t>
+          <t>1276; 7306</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3124; 10867</t>
+          <t>1521; 8522</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>692; 6592</t>
+          <t>846; 7152</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3234; 11278</t>
+          <t>3294; 10930</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6323; 17173</t>
+          <t>6044; 16026</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2894; 11188</t>
+          <t>2825; 11984</t>
         </is>
       </c>
     </row>
